--- a/data/trans_orig/P41C_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P41C_R-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dificultades para tener un embarazo en 2023</t>
+          <t>Población con dificultades para tener un embarazo en 2023 (tasa de respuesta: 87,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1249</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1886</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3962</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>9,06%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1249</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3954</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4145</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>9,05%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1249</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4617</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46434</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48320</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39758</t>
+          <t>39750</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>87415</t>
+          <t>87887</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4492</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31631</t>
+          <t>30620</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7912</t>
+          <t>7596</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19996</t>
+          <t>19767</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14815</t>
+          <t>14245</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43373</t>
+          <t>43268</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>641400</t>
+          <t>642411</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>668539</t>
+          <t>668193</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>448698</t>
+          <t>448927</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>460782</t>
+          <t>461098</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1098352</t>
+          <t>1098457</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1126910</t>
+          <t>1127480</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>4625</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21735</t>
+          <t>21142</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9834</t>
+          <t>9727</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23006</t>
+          <t>23224</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17245</t>
+          <t>17356</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38315</t>
+          <t>37734</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>136171</t>
+          <t>136764</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>153328</t>
+          <t>153281</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159867</t>
+          <t>159649</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>173039</t>
+          <t>173146</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>302463</t>
+          <t>303044</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>323533</t>
+          <t>323422</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,91%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11166</t>
+          <t>9236</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46217</t>
+          <t>46111</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21071</t>
+          <t>21409</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39850</t>
+          <t>40083</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32861</t>
+          <t>35138</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75203</t>
+          <t>74554</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>833040</t>
+          <t>833146</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>868091</t>
+          <t>870021</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>655429</t>
+          <t>655196</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>674208</t>
+          <t>673870</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1499332</t>
+          <t>1499981</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1541674</t>
+          <t>1539397</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P41C_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P41C_R-Estudios-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t>5219</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>48320</t>
+          <t>54242</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>42463</t>
+          <t>49260</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39750</t>
+          <t>46425</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43712</t>
+          <t>50531</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>90783</t>
+          <t>103502</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>87887</t>
+          <t>99554</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>92032</t>
+          <t>104773</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>48320</t>
+          <t>54242</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48320</t>
+          <t>54242</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48320</t>
+          <t>54242</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>43712</t>
+          <t>50531</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>43712</t>
+          <t>50531</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43712</t>
+          <t>50531</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>92032</t>
+          <t>104773</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>92032</t>
+          <t>104773</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>92032</t>
+          <t>104773</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15937</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>10346</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30620</t>
+          <t>27772</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12815</t>
+          <t>14644</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7596</t>
+          <t>9254</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19767</t>
+          <t>22309</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>28752</t>
+          <t>31973</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14245</t>
+          <t>22710</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43268</t>
+          <t>43461</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>657094</t>
+          <t>449806</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>642411</t>
+          <t>439363</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>668193</t>
+          <t>456789</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>455879</t>
+          <t>504544</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>448927</t>
+          <t>496879</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>461098</t>
+          <t>509934</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1112973</t>
+          <t>954350</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1098457</t>
+          <t>942862</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1127480</t>
+          <t>963613</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>97,7%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>673031</t>
+          <t>467135</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>673031</t>
+          <t>467135</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>673031</t>
+          <t>467135</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>468694</t>
+          <t>519188</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>468694</t>
+          <t>519188</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>468694</t>
+          <t>519188</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1141725</t>
+          <t>986323</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1141725</t>
+          <t>986323</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1141725</t>
+          <t>986323</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10555</t>
+          <t>11227</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4625</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21142</t>
+          <t>24131</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15374</t>
+          <t>15854</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>9474</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23224</t>
+          <t>23676</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>25928</t>
+          <t>27081</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17356</t>
+          <t>17743</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37734</t>
+          <t>40324</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>147351</t>
+          <t>161960</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>136764</t>
+          <t>149056</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>153281</t>
+          <t>168037</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>167499</t>
+          <t>188024</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159649</t>
+          <t>180202</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>173146</t>
+          <t>194404</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>314850</t>
+          <t>349984</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>303044</t>
+          <t>336741</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>323422</t>
+          <t>359322</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>157906</t>
+          <t>173187</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>157906</t>
+          <t>173187</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>157906</t>
+          <t>173187</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182873</t>
+          <t>203878</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182873</t>
+          <t>203878</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182873</t>
+          <t>203878</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>340778</t>
+          <t>377065</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>340778</t>
+          <t>377065</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>340778</t>
+          <t>377065</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26491</t>
+          <t>28556</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9236</t>
+          <t>18331</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46111</t>
+          <t>44366</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29437</t>
+          <t>31769</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21409</t>
+          <t>23090</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40083</t>
+          <t>42269</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>55929</t>
+          <t>60325</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35138</t>
+          <t>46634</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74554</t>
+          <t>79938</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>852766</t>
+          <t>666008</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>833146</t>
+          <t>650198</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>870021</t>
+          <t>676233</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>665842</t>
+          <t>741827</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>655196</t>
+          <t>731327</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>673870</t>
+          <t>750506</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1518606</t>
+          <t>1407836</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1499981</t>
+          <t>1388223</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1539397</t>
+          <t>1421527</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>879257</t>
+          <t>694564</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>879257</t>
+          <t>694564</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>879257</t>
+          <t>694564</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>695279</t>
+          <t>773596</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>695279</t>
+          <t>773596</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>695279</t>
+          <t>773596</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1574535</t>
+          <t>1468161</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1574535</t>
+          <t>1468161</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1574535</t>
+          <t>1468161</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
